--- a/data/trans_dic/IP31KM04_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP31KM04_2023-Estudios-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>50,08%</t>
+          <t>52,61%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>52,35%</t>
+          <t>56,19%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>51,26%</t>
+          <t>54,26%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>32,73; 65,48</t>
+          <t>40,93; 64,37</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>39,98; 63,54</t>
+          <t>44,05; 68,44</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>40,77; 61,11</t>
+          <t>45,43; 63,31</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>40,8%</t>
+          <t>45,53%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>45,87%</t>
+          <t>43,14%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>43,48%</t>
+          <t>44,39%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>33,01; 45,16</t>
+          <t>41,41; 50,53</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>40,86; 50,85</t>
+          <t>39,05; 47,32</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>39,04; 47,3</t>
+          <t>41,1; 47,44</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>44,75%</t>
+          <t>47,81%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>46,48%</t>
+          <t>45,61%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>45,71%</t>
+          <t>46,77%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>38,15; 51,24</t>
+          <t>40,51; 54,09</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>39,64; 53,95</t>
+          <t>38,63; 52,42</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>40,99; 50,72</t>
+          <t>42,02; 51,75</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>42,45%</t>
+          <t>46,63%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>46,53%</t>
+          <t>44,7%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>44,62%</t>
+          <t>45,72%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>36,55; 46,61</t>
+          <t>43,48; 50,47</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>42,44; 50,23</t>
+          <t>41,28; 48,09</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>41,37; 47,5</t>
+          <t>43,24; 48,4</t>
         </is>
       </c>
     </row>
@@ -780,12 +780,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -833,12 +833,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>35</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -856,17 +856,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>26891</t>
+          <t>28259</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>30545</t>
+          <t>25795</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>57435</t>
+          <t>54054</t>
         </is>
       </c>
     </row>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>17578; 35163</t>
+          <t>21988; 34576</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>23324; 37070</t>
+          <t>20220; 31416</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>45678; 68465</t>
+          <t>45258; 63072</t>
         </is>
       </c>
     </row>
@@ -906,12 +906,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>285</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>270</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>285</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -929,17 +929,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>184339</t>
+          <t>212354</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>231773</t>
+          <t>183195</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>416112</t>
+          <t>395550</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>149140; 204068</t>
+          <t>193168; 235675</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>206447; 256924</t>
+          <t>165853; 200936</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>373606; 452662</t>
+          <t>366277; 422692</t>
         </is>
       </c>
     </row>
@@ -979,12 +979,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>102</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>112</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1002,17 +1002,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>65417</t>
+          <t>79686</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>84196</t>
+          <t>67103</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>149613</t>
+          <t>146788</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>55764; 74906</t>
+          <t>67533; 90154</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>71810; 97725</t>
+          <t>56840; 77137</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>134185; 166008</t>
+          <t>131860; 162397</t>
         </is>
       </c>
     </row>
@@ -1052,12 +1052,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>437</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>407</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>437</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1075,17 +1075,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>276647</t>
+          <t>320299</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>346514</t>
+          <t>276094</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>623161</t>
+          <t>596392</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>238232; 303764</t>
+          <t>298651; 346673</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>316080; 374094</t>
+          <t>254982; 297048</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>577764; 663302</t>
+          <t>564104; 631341</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP31KM04_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP31KM04_2023-Estudios-trans_dic.xlsx
@@ -17,7 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -98,7 +100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -111,6 +113,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -477,290 +485,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Menores que toman verduras frescas o cocinadas más de una vez al día (tasa de respuesta: 100,0%)</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niña</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="n"/>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" hidden="1">
-      <c r="A3" s="4" t="n"/>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>Primarios</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>52,61%</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>56,19%</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>54,26%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n"/>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>40,93; 64,37</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>44,05; 68,44</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>45,43; 63,31</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>Secundarios</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>45,53%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>43,14%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>44,39%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>41,41; 50,53</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>39,05; 47,32</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>41,1; 47,44</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Universitarios</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>47,81%</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>45,61%</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>46,77%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n"/>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>40,51; 54,09</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>38,63; 52,42</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>42,02; 51,75</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>46,63%</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>44,7%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>45,72%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n"/>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>43,48; 50,47</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>41,28; 48,09</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>43,24; 48,4</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -828,69 +552,51 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>0.5260969292925611</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.5619211115801926</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.5426047532850303</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>28259</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>25795</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>54054</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>0.4093402479299282</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>0.4404753445002644</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>0.4543072821848267</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>21988; 34576</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>20220; 31416</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>45258; 63072</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>0.6436959385477005</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>0.6843747081819468</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0.6331301979551079</v>
       </c>
     </row>
     <row r="7">
@@ -901,69 +607,51 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>285</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>270</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>555</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>0.4552814427565174</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.4313872301250055</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.4438941842115207</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>212354</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>183195</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>395550</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>0.4141469827187494</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0.3905498992079211</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0.4110442910274459</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>193168; 235675</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>165853; 200936</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>366277; 422692</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0.5052810113525196</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0.47316139221041</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0.4743543121986439</v>
       </c>
     </row>
     <row r="10">
@@ -974,69 +662,51 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>112</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>102</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>214</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>0.4780576855844053</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.4560508493735767</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.4677395895124236</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>79686</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>67103</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>146788</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0.4051490315642188</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0.3862993127717471</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>0.420169624987668</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>67533; 90154</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>56840; 77137</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>131860; 162397</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0.5408584287736187</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0.5242400963816215</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0.5174778894586586</v>
       </c>
     </row>
     <row r="13">
@@ -1047,69 +717,51 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>437</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>407</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>844</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.4663473195374052</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.4469626839580152</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.4571684897013399</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>320299</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>276094</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>596392</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>0.4348287894640795</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>0.4127847357915655</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>0.4324178347758476</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>298651; 346673</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>254982; 297048</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>564104; 631341</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0.5047485719750419</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0.4808851426684969</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0.4839590341588362</v>
       </c>
     </row>
     <row r="16">
@@ -1129,4 +781,376 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que toman verduras frescas o cocinadas más de una vez al día (tasa de respuesta: 100,0%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Primarios</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>40</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>35</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>28259</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>25795</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>54054</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>21988</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>20220</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>45258</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n"/>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>34576</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>31416</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>63072</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>285</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>270</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>212354</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>183195</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>395550</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n"/>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>193168</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>165853</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>366277</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>235675</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>200936</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>422692</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>Universitarios</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>112</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>102</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>79686</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>67103</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>146788</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>67533</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>56840</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>131860</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>90154</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>77137</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>162397</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>437</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>407</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>844</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>320299</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>276094</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>596392</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>298651</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>254982</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>564104</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n"/>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>346673</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>297048</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>631341</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A16:A19"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>